--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260201_201356.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260201_201356.xlsx
@@ -4656,7 +4656,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5006,7 +5006,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260201_201356.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260201_201356.xlsx
@@ -4656,7 +4656,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5006,7 +5006,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
